--- a/projects/components/ecc-ip/bch/docs/bch_signal_contracts.xlsx
+++ b/projects/components/ecc-ip/bch/docs/bch_signal_contracts.xlsx
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>rtl/bch_encoder_core.sv</t>
+          <t>rtl/macro/bch_encoder_core.sv</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>rtl/bch_syndrome_unit.sv</t>
+          <t>rtl/fub/bch_syndrome_unit.sv</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>rtl/bch_chien_search.sv</t>
+          <t>rtl/fub/bch_chien_search.sv</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>rtl/bch_decoder_core.sv</t>
+          <t>rtl/macro/bch_decoder_core.sv</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>rtl/bch_encoder_core.sv / rtl/bch_decoder_core.sv</t>
+          <t>rtl/macro/bch_encoder_core.sv / rtl/macro/bch_decoder_core.sv</t>
         </is>
       </c>
     </row>

--- a/projects/components/ecc-ip/bch/docs/bch_signal_contracts.xlsx
+++ b/projects/components/ecc-ip/bch/docs/bch_signal_contracts.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core signals" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K-maps BCH qualifiers" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract posture" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Citation posture" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -493,14 +493,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BCH core valid/ready signal contract (pre-RTL, cites MAS pages)</t>
+          <t>BCH core valid/ready signal contract (cites landed RTL)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The core presents the house valid/ready contract at both ends. Widths and reset values are parametric; behavior is tied to the MAS block pages. Sources: projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md, projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/02_syndrome_unit.md, projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/04_chien_search.md, projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/05_decoder_core.md, projects/components/ecc-ip/bch/docs/bch_mas/ch03_interfaces/01_core_signals.md.</t>
+          <t>The core presents the house valid/ready contract at both ends. Widths and reset values are parametric; behavior cites the landed RTL file:line and the citation gate fails the build on drift. Sources: projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv, projects/components/ecc-ip/bch/rtl/fub/bch_syndrome_unit.sv, projects/components/ecc-ip/bch/rtl/fub/bch_chien_search.sv, projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv, projects/components/ecc-ip/bch/docs/bch_mas/ch03_interfaces/01_core_signals.md.</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:interface table</t>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:77</t>
         </is>
       </c>
     </row>
@@ -621,12 +621,12 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>combinational !r_valid || m_ready</t>
+          <t>low only while the parity-shift DRAIN state drains the skid</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:interface table</t>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:206</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:interface table</t>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:79</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:interface table</t>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:80</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:interface table</t>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:81</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:interface table</t>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:83</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:109</t>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:244, projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:247, projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:308</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:129</t>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:227</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>in_last &amp;&amp; (r_bit_count != K_BITS - 1)</t>
+          <t>in_last &amp;&amp; ((r_data_count + w_in_count) != K)</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:164</t>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:228</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>ready drops when buffer full</t>
+          <t>ready drops outside SYND and once the block is ending; over-N blocks are still accepted so the sender can reach in_last (issue #90)</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/05_decoder_core.md:interface table</t>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:95, projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:96, projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:370</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/05_decoder_core.md:interface table</t>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:99</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>high only after verdict final</t>
+          <t>high only in RELEASE, per beat</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/05_decoder_core.md:interface table</t>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:411</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>uncorrectable block leaves as received</t>
+          <t>uncorrectable block leaves as received (r_release_apply = 0)</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/05_decoder_core.md:91</t>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:413</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/05_decoder_core.md:interface table</t>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:414</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/02_syndrome_unit.md:109</t>
+          <t>projects/components/ecc-ip/bch/rtl/fub/bch_syndrome_unit.sv:162, projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:417</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>held for every beat of the block</t>
+          <t>the Chien root count of a correctable block</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/04_chien_search.md:115</t>
+          <t>projects/components/ecc-ip/bch/rtl/fub/bch_chien_search.sv:231, projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:418</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>!w_correctable or recheck non-zero</t>
+          <t>!w_verdict_correctable out of CHIEN/RECHECK</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/05_decoder_core.md:126</t>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:396, projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:419</t>
         </is>
       </c>
     </row>
@@ -1288,17 +1288,17 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>block length was not N_BITS</t>
+          <t>block length was not N_BITS (short, long, or over-N runaway)</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>held for every beat of the block</t>
+          <t>held for every beat of the block; issue #90 released the over-N prefix as frame_err</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/05_decoder_core.md:interface table</t>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:337, projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:420</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D167"/>
+  <dimension ref="A1:D170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1329,1429 +1329,1477 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BCH codec - decision K-maps (pre-RTL, citations point at MAS pages)</t>
+          <t>BCH codec - decision K-maps (citations point at landed RTL)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Each table is computed from a Python mirror of the intended expression</t>
+          <t>Each table is computed from a Python mirror of the landed expression</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cited in the MAS. The verdict is NOT CHECKED because no RTL exists yet.</t>
+          <t>and every citation is gated: verify_citations fails the build if the</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>When RTL lands, the citations are re-pointed at .sv file:line and the</t>
+          <t>RTL moves under a quoted line. Each map's rtl_sop is the RTL as</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>verdict becomes meaningful.</t>
+          <t>written, so the VERDICT line is the derived minimal cover diffed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>against the silicon-intended logic (IDENTICAL, or DIFFERS with the</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>reconciliation cases spelled out).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>w_parity_phase</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:109</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>w_parity_phase = (r_bit_count &gt;= K_BITS) &amp;&amp; w_beat_is_parity</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rows = bit_ge_k/beat_is_parity   cols = </t>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:226</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): parity is selected only after the data phase ends AND the current output beat carries at least one parity bit.</t>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>w_parity_phase = r_drain || ((r_bit_count &gt;= K_BITS) &amp;&amp; w_beat_is_parity)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>rows = r_drain/bit_ge_k   cols = beat_is_parity</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: 1s on the whole r_drain=1 page plus the single (0,1,1) cell: parity is selected during the DRAIN state, or once the data phase has ended AND the current output beat carries at least one parity bit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>AXES</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>axis</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>defining expression</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>cite</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>r_drain</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>r_drain -- the parity shift-out state</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>bit_ge_k</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>r_bit_count &gt;= K_BITS</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:109</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:226</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>beat_is_parity</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>w_beat_is_parity = (r_bit_count + BITS_PER_BEAT - 1) &gt;= K_BITS</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:116</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: these two. K_BITS and BITS_PER_BEAT are elaboration-time constants; the bit counter is the only runtime variable feeding both terms. The mux data/parity payload does not gate the phase select.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:225</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>0</v>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these three. K_BITS and BITS_PER_BEAT are elaboration-time constants; r_bit_count and r_drain are the only runtime state. w_beat_is_parity is a full-B lookahead (the RTL comment at the cite says so), which is why the phase can rise a beat early without emitting parity early: the payload mux (the DRAIN/output-select block) still gates what leaves. The pre-RTL MAS had no r_drain term -- the encoder shifts parity out of the skid buffer after in_last, and the drain state forces the phase for those beats.</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="n">
-        <v>1</v>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>DERIVED MINIMAL SOP: bit_ge_k &amp; beat_is_parity</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>RTL AS WRITTEN:      bit_ge_k &amp; beat_is_parity</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="B24" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: bit_ge_k &amp; beat_is_parity  |  r_drain</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      r_drain | bit_ge_k &amp; beat_is_parity</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>w_enc_out_last</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:129</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>w_enc_out_last = w_parity_phase &amp;&amp; (r_parity_count == N_BITS - K_BITS - 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:227</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>w_enc_out_last = w_parity_phase &amp;&amp; ((r_parity_count + w_par_beat_len - 1) == N_BITS - K_BITS - 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = parity_phase/last_parity   cols = </t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): the final coded bit leaves only during the parity phase when the last parity symbol is being emitted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): the final coded bit leaves only during the parity phase on the beat whose last parity bit is the N_BITS-th coded bit. r_parity_count + w_par_beat_len is the lookahead end of the current beat, the beat-granular twin of the MAS's per-bit count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>AXES</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>axis</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>defining expression</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>cite</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>parity_phase</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>w_parity_phase</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:109</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:226</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>last_parity</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>r_parity_count == N_BITS - K_BITS - 1</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:129</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>r_parity_count + w_par_beat_len - 1 == N_BITS - K_BITS - 1</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:227</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>DEPENDS ONLY ON: these two. The bit counter value and the parity count are the only runtime state; N_BITS and K_BITS are elaboration constants. The output beat payload does not gate out_last.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="9" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B41" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="B44" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: parity_phase &amp; last_parity</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>RTL AS WRITTEN:      parity_phase &amp; last_parity</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
         <is>
           <t>w_frame_err (encoder)</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:164</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>w_frame_err = in_last &amp;&amp; (r_bit_count != K_BITS - 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:228</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>w_frame_err = in_last &amp;&amp; ((r_data_count + w_in_count) != K_BITS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = in_last/wrong_length   cols = </t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): a block boundary that does not coincide with the K_BITS-th data bit is a framing error (R1/R2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): a block boundary that does not coincide with the K_BITS-th data bit is a framing error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>AXES</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>axis</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>defining expression</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>cite</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>in_last</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>in_last</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:164</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:228</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>wrong_length</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>r_bit_count != K_BITS - 1</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:164</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: these two. K_BITS is an elaboration constant; the bit counter and the in_last flag are the runtime inputs. No other encoder signal can create or suppress a frame error.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>r_data_count + w_in_count != K_BITS</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_encoder_core.sv:228</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these two. K_BITS is an elaboration constant; r_data_count is the accepted-data count and w_in_count the presenting beat's keep count, so the check sees the would-be block total on the boundary cycle. No other encoder signal can create or suppress a frame error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B60" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B61" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="B64" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: in_last &amp; wrong_length</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>RTL AS WRITTEN:      in_last &amp; wrong_length</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
         <is>
           <t>w_syndrome_done</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/02_syndrome_unit.md:121</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>w_syndrome_done = (r_bit_count == N_BITS - 1) &amp;&amp; in_valid &amp;&amp; in_ready</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/fub/bch_syndrome_unit.sv:157</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>w_syndrome_done = w_last_bit &amp;&amp; in_valid &amp;&amp; in_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>rows = last_bit/in_valid   cols = in_ready</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1): the syndrome unit completes only on the cycle the final bit is accepted. A last-bit cycle without a handshake does not complete the syndromes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1): the syndrome unit completes only on the cycle the final bit is accepted. A last-bit cycle without a handshake does not complete the syndromes, and the decoder core only consumes the result once the block boundary has arrived (its w_synd_result_valid waits for in_last).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>AXES</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>axis</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>defining expression</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>cite</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>last_bit</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>r_bit_count == N_BITS - 1</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/02_syndrome_unit.md:121</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>w_last_bit = (r_bit_count + w_in_count == N_BITS)</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/fub/bch_syndrome_unit.sv:156</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>in_valid</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>in_valid</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/02_syndrome_unit.md:121</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/fub/bch_syndrome_unit.sv:157</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>in_ready</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>in_ready</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/02_syndrome_unit.md:121</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/fub/bch_syndrome_unit.sv:157</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>DEPENDS ONLY ON: these three. N_BITS is an elaboration constant; the bit counter, the offered valid, and the accepted ready are the only runtime inputs. The syndrome lane values do not gate completion.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="9" t="inlineStr">
+    <row r="81">
+      <c r="B81" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B79" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B80" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C80" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B81" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B82" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C82" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
+      <c r="B85" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: last_bit &amp; in_valid &amp; in_ready</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>RTL AS WRITTEN:      last_bit &amp; in_valid &amp; in_ready</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="12" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
         <is>
           <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="1" t="inlineStr">
-        <is>
-          <t>w_no_error</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/02_syndrome_unit.md:109</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>w_no_error = (S_1 == 0) &amp;&amp; (S_3 == 0) &amp;&amp; ... &amp;&amp; (S_2t-1 == 0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>out_no_error</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/fub/bch_syndrome_unit.sv:162</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>out_no_error = (out_syndromes == '0)   -- S_1 == 0 &amp;&amp; S_3 == 0 &amp;&amp; ... &amp;&amp; S_2t-1 == 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = S_1_zero/S_rest_zero   cols = </t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): all odd syndromes zero means the block has no detectable errors and the decoder can bypass solve and Chien.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="8" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): all odd syndromes zero means the block has no detectable errors and the decoder bypasses solve and Chien. The RTL compares the whole packed syndrome vector in one expression; the two axes are a factoring of that comparison (S_1 and the rest), not two separate hardware terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
         <is>
           <t>AXES</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="8" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>axis</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>defining expression</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>cite</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>S_1_zero</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>S_1 == 0</t>
         </is>
       </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/02_syndrome_unit.md:109</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/fub/bch_syndrome_unit.sv:162</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>S_rest_zero</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>(S_3 == 0) &amp;&amp; ... &amp;&amp; (S_2t-1 == 0)</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/02_syndrome_unit.md:109</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: these two (a factoring of the t odd syndromes into S_1 and the rest). The evenness shortcut means even syndromes are derived, not inputs. No block-boundary or status signal gates the no-error decode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="9" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/fub/bch_syndrome_unit.sv:162</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these two (a factoring of the t odd syndromes into S_1 and the rest). The evenness shortcut means even syndromes are derived, not stored. No block-boundary or status signal gates the no-error decode; the register is stable from completion per the fub header.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B99" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B100" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B101" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B102" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="6" t="inlineStr">
+      <c r="B105" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: S_1_zero &amp; S_rest_zero</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>RTL AS WRITTEN:      S_1_zero &amp; S_rest_zero</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="12" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
         <is>
           <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="1" t="inlineStr">
-        <is>
-          <t>w_correctable</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/05_decoder_core.md:127</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>w_correctable = (r_root_count == r_lambda_degree) &amp;&amp; (r_lambda_degree &lt;= T_BITS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rows = root_count_match/degree_ok   cols = </t>
-        </is>
-      </c>
-    </row>
     <row r="111">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): a block is correctable only when every root of Lambda is found (root count equals degree) and the degree is within the code's correction capability.</t>
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>w_verdict_correctable</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:396</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="inlineStr">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>w_verdict_correctable = !r_more_than_t &amp;&amp; (root_count == r_lambda_degree) &amp;&amp; (!ENABLE_RECHECK || w_rechk_out_no_error)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>rows = not_more_than_t/root_count_match   cols = recheck_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1): a block is correctable only when the solver degree is within t, every root of Lambda was found, and the re-check syndromes of the corrected buffer are all zero. The map holds ENABLE_RECHECK = 1 (the default); with it 0 the recheck_ok axis is the constant 1 and the map collapses to the first two axes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
         <is>
           <t>AXES</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="8" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
         <is>
           <t>axis</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>defining expression</t>
         </is>
       </c>
-      <c r="D113" s="8" t="inlineStr">
+      <c r="D116" s="8" t="inlineStr">
         <is>
           <t>cite</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>not_more_than_t</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>!r_more_than_t -- solver degree within t</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:396</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>root_count_match</t>
         </is>
       </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>r_root_count == r_lambda_degree</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/05_decoder_core.md:127</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>degree_ok</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>r_lambda_degree &lt;= T_BITS</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/05_decoder_core.md:127</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: these two. T_BITS is an elaboration constant; the root count and locator degree are produced by the Chien search and the solver. The original syndromes influence the result only through those two values.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" s="9" t="inlineStr">
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>root_count == r_lambda_degree</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:397</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>recheck_ok</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>!ENABLE_RECHECK || w_rechk_out_no_error</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:399</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these three. r_more_than_t and r_lambda_degree come from the solver (captured at SOLVE done), the root count is the Chien total -- the CHIEN/RECHECK mux in the RTL selects the live count in CHIEN and the value captured at the last beat in RECHECK, the same value at the decision points. The original syndromes influence the verdict only through these three terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: not_more_than_t &amp; root_count_match &amp; recheck_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      not_more_than_t &amp; root_count_match &amp; recheck_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="12" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>out_flip_en (Chien)</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/fub/bch_chien_search.sv:230</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>out_flip_en[i] = w_root[i] &amp;&amp; w_pos_valid[i]</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rows = root/pos_valid   cols = </t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): a flip is flagged only at a root position inside the block length. Beyond n (a shortened code's tail beats) the lanes are masked off so the root count and the flip mask cannot leak into padding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>w_root[i] = (Lambda(alpha^-i) == 0)</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/fub/bch_chien_search.sv:206</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>pos_valid</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>w_pos_valid[i] = (r_position + i) &lt; N_BITS</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/fub/bch_chien_search.sv:212</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these two, per lane. The pre-RTL design folded the correctable and pass-through gating into this signal; the landed core separates concerns -- this is the raw per-beat flip map, the verdict gating is registered per block as r_release_apply (decoder core) and applied on the way out. Binary codes flip, never scale: there is no Forney stage and no magnitude.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B119" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B120" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B121" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B122" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>DERIVED MINIMAL SOP: root_count_match &amp; degree_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>RTL AS WRITTEN:      root_count_match &amp; degree_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="12" t="inlineStr">
-        <is>
-          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="1" t="inlineStr">
-        <is>
-          <t>w_flip_en[i]</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/04_chien_search.md:102</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>w_flip_en[i] = w_root[i] &amp;&amp; w_correctable &amp;&amp; !w_release_passthrough</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>rows = root/correctable   cols = not_passthrough</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1): a bit is flipped only at a root position, in a correctable block, when the block is not being passed through unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="8" t="inlineStr">
-        <is>
-          <t>AXES</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="8" t="inlineStr">
-        <is>
-          <t>axis</t>
-        </is>
-      </c>
-      <c r="B133" s="8" t="inlineStr">
-        <is>
-          <t>defining expression</t>
-        </is>
-      </c>
-      <c r="D133" s="8" t="inlineStr">
-        <is>
-          <t>cite</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>root</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>w_root[i] = (Lambda(alpha^-i) == 0)</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/04_chien_search.md:102</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>correctable</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>w_correctable</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/05_decoder_core.md:127</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>not_passthrough</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>!w_release_passthrough</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/05_decoder_core.md:91</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: these three. The root flag is per-position; correctable and release_passthrough are per-block qualifiers. No error value is computed — binary codes always flip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="B139" s="9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C139" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B140" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C140" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B141" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C141" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B142" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C142" s="10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B143" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B143" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C143" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>DERIVED MINIMAL SOP: root &amp; correctable &amp; !not_passthrough</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>RTL AS WRITTEN:      root &amp; correctable &amp; !not_passthrough</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="12" t="inlineStr">
+      <c r="B146" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: root &amp; pos_valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      root &amp; pos_valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="12" t="inlineStr">
         <is>
           <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="1" t="inlineStr">
-        <is>
-          <t>w_release_passthrough</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/05_decoder_core.md:91</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="6" t="inlineStr">
-        <is>
-          <t>w_release_passthrough = w_uncorrectable || w_frame_err</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rows = uncorrectable/frame_err   cols = </t>
-        </is>
-      </c>
-    </row>
     <row r="152">
-      <c r="A152" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: 1s everywhere except (0,0): an uncorrectable block or a frame-error block leaves the buffer exactly as received (R2).</t>
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>out_data correction gating</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:413</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="8" t="inlineStr">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>out_data = r_buf[r_release_idx] ^ (r_flip[r_release_idx] &amp; {B{r_release_apply}})</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rows = flip/apply   cols = </t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): a buffered bit changes only where the Chien search flagged a root AND the final verdict says correctable. Every other combination leaves the buffer bit-for-bit -- that is the uncorrectable / frame-err pass-through (the core header's 'never silently pass a failed block' property).</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="inlineStr">
         <is>
           <t>AXES</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="8" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="8" t="inlineStr">
         <is>
           <t>axis</t>
         </is>
       </c>
-      <c r="B154" s="8" t="inlineStr">
+      <c r="B157" s="8" t="inlineStr">
         <is>
           <t>defining expression</t>
         </is>
       </c>
-      <c r="D154" s="8" t="inlineStr">
+      <c r="D157" s="8" t="inlineStr">
         <is>
           <t>cite</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="5" t="inlineStr">
-        <is>
-          <t>uncorrectable</t>
-        </is>
-      </c>
-      <c r="B155" s="6" t="inlineStr">
-        <is>
-          <t>w_uncorrectable</t>
-        </is>
-      </c>
-      <c r="D155" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/05_decoder_core.md:126</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="5" t="inlineStr">
-        <is>
-          <t>frame_err</t>
-        </is>
-      </c>
-      <c r="B156" s="6" t="inlineStr">
-        <is>
-          <t>w_frame_err</t>
-        </is>
-      </c>
-      <c r="D156" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md:164 / decoder analog</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: these two. The pass-through decision is per-block; the Chien position and the individual root flags do not gate it. A block can be both uncorrectable and frame-erroneous, and the result is the same.</t>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>flip</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>r_flip[r_release_idx] -- the Chien beat map, registered during CHIEN</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:579</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="B159" s="9" t="inlineStr">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>r_release_apply -- w_verdict_correctable registered at decision</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/ecc-ip/bch/rtl/macro/bch_decoder_core.sv:592</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these two. r_flip was captured per beat while the Chien search walked the block; r_release_apply is the registered verdict, so the gating cannot change mid-release. The release index and keep logic select which buffered beat and lanes leave, not whether the correction applies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B160" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B161" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B162" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B163" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B164" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B165" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B163" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="6" t="inlineStr">
-        <is>
-          <t>DERIVED MINIMAL SOP: frame_err  |  uncorrectable</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="5" t="inlineStr">
-        <is>
-          <t>RTL AS WRITTEN:      uncorrectable | frame_err</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="12" t="inlineStr">
+      <c r="B166" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: flip &amp; apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      flip &amp; apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="12" t="inlineStr">
         <is>
           <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
         </is>
@@ -2768,7 +2816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2784,149 +2832,177 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Pre-RTL citation posture</t>
+          <t>Citation posture (post-RTL)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The workbook cites the MAS pages where the intended expressions are</t>
+          <t>Migrated 2026-10-08 with the TASK-003 close: every workbook citation</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>written verbatim. When RTL lands, every MAS citation is re-pointed at</t>
+          <t>moved from the pre-RTL MAS pages to the landed RTL file:line. The</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>the relevant .sv file:line and verify_citations will catch drift.</t>
+          <t>verify_citations gate at build time fails the generator if any RTL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>edit moves a quoted line, so the workbook cannot drift stale.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Citation migration plan</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>MAS pages -&gt; RTL files</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Kmap verdicts render IDENTICAL / DIFFERS from the rtl_sop diff; all</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>All verdicts render NOT CHECKED until the RTL citations land.</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>eight maps of the landed design render IDENTICAL (the RTL is already</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>minimal for every mapped qualifier).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Citation migration record</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>MAS pages -&gt; RTL files (done 2026-10-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>The MAS pages remain the methodology authority; the workbook cites silicon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>MAS page</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>current citation target</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>future RTL target</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Encoder core</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/01_encoder.md</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>rtl/macro/bch_encoder_core.sv</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Syndrome unit</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/02_syndrome_unit.md</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>rtl/fub/bch_syndrome_unit.sv</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Chien search</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/04_chien_search.md</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>rtl/fub/bch_chien_search.sv</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Decoder core</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch02_blocks/05_decoder_core.md</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>rtl/macro/bch_decoder_core.sv</t>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>pre-RTL citation target</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>RTL target since migration</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>Encoder core</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>docs/bch_mas/ch02_blocks/01_encoder.md</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>rtl/macro/bch_encoder_core.sv</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Syndrome unit</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>docs/bch_mas/ch02_blocks/02_syndrome_unit.md</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>rtl/fub/bch_syndrome_unit.sv</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Chien search</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>docs/bch_mas/ch02_blocks/04_chien_search.md</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>rtl/fub/bch_chien_search.sv</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Decoder core</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>docs/bch_mas/ch02_blocks/05_decoder_core.md</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>rtl/macro/bch_decoder_core.sv</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>Core signals</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>projects/components/ecc-ip/bch/docs/bch_mas/ch03_interfaces/01_core_signals.md</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>rtl/macro/bch_encoder_core.sv / rtl/macro/bch_decoder_core.sv</t>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>docs/bch_mas/ch03_interfaces/01_core_signals.md</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>both core .sv files (reset posture stays with the MAS page)</t>
         </is>
       </c>
     </row>
